--- a/resources/templates/heyman/power_of_attorney.xlsx
+++ b/resources/templates/heyman/power_of_attorney.xlsx
@@ -156,7 +156,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">  경기도 시흥시 산기대학로 163, A동 328호(정왕동)</t>
+      <t xml:space="preserve">  서울특별시 영등포구 선유동1로 50, 513호(당산동3가, THE PARK 365)</t>
     </r>
   </si>
   <si>
@@ -1232,7 +1232,7 @@
       <c r="C24" s="19" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">  경기도 시흥시 산기대학로 163, A동 328호(정왕동)</t>
+            <t xml:space="preserve">  서울특별시 영등포구 선유동1로 50, 513호(당산동3가, THE PARK 365)</t>
           </r>
         </is>
       </c>

--- a/resources/templates/heyman/power_of_attorney.xlsx
+++ b/resources/templates/heyman/power_of_attorney.xlsx
@@ -161,7 +161,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">120111-0922270</t>
+      <t xml:space="preserve">110111-7526176</t>
     </r>
   </si>
   <si>
@@ -1261,7 +1261,7 @@
       <c r="C25" s="25" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">120111-0922270</t>
+            <t xml:space="preserve">110111-7526176</t>
           </r>
         </is>
       </c>
